--- a/output/frequent_itemsets.xlsx
+++ b/output/frequent_itemsets.xlsx
@@ -552,7 +552,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'operator_Anisa'})</t>
+          <t>frozenset({'operator_Anisa', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'operator_Anisa'})</t>
+          <t>frozenset({'operator_Anisa', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>frozenset({'produk_night cream brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_hb dosting 75 gram'})</t>
+          <t>frozenset({'produk_hb dosting 75 gram', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_sunscreen oily acne new'})</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_hb dosting 75 gram'})</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frozenset({'produk_paket brightening', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_paket brightening'})</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_paket acne 1'})</t>
+          <t>frozenset({'produk_paket acne 1', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'waktu_Siang'})</t>
+          <t>frozenset({'waktu_Siang', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_sunscreen glowing new'})</t>
+          <t>frozenset({'produk_sunscreen glowing new', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>frozenset({'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml'})</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>frozenset({'produk_serum brightening glowing', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_serum brightening glowing'})</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_sunscreen natural glow for normal skin new'})</t>
+          <t>frozenset({'produk_sunscreen natural glow for normal skin new', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_paket custom'})</t>
+          <t>frozenset({'produk_paket custom', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Malam'})</t>
+          <t>frozenset({'waktu_Malam', 'produk_daily ceramois hydra gel'})</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_sunscreen glowing new'})</t>
+          <t>frozenset({'produk_sunscreen glowing new', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'produk_facial wash oily acne 110 ml new'})</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen glowing new'})</t>
+          <t>frozenset({'produk_sunscreen glowing new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">

--- a/output/frequent_itemsets.xlsx
+++ b/output/frequent_itemsets.xlsx
@@ -624,7 +624,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Indah'})</t>
+          <t>frozenset({'operator_Indah', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'operator_Riska'})</t>
+          <t>frozenset({'operator_Riska', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Anisa', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'operator_Anisa'})</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_night cream brightening'})</t>
+          <t>frozenset({'produk_night cream brightening', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_hb dosting 75 gram'})</t>
+          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Pagi', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Pagi'})</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_hb dosting 75 gram'})</t>
+          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Oktavira', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Oktavira'})</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Riska', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Riska'})</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_hb dosting 75 gram'})</t>
+          <t>frozenset({'produk_hb dosting 75 gram', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Siang', 'produk_serum brightening glowing'})</t>
+          <t>frozenset({'produk_serum brightening glowing', 'waktu_Siang'})</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml'})</t>
+          <t>frozenset({'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_serum brightening glowing'})</t>
+          <t>frozenset({'produk_serum brightening glowing', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>frozenset({'produk_night cream brightening', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'produk_night cream brightening'})</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_paket brightening'})</t>
+          <t>frozenset({'produk_paket brightening', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_sunscreen oily acne new'})</t>
+          <t>frozenset({'produk_sunscreen oily acne new', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml'})</t>
+          <t>frozenset({'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>frozenset({'produk_radian brightening ultimate', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_radian brightening ultimate'})</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_daily ceramois hydra gel'})</t>
+          <t>frozenset({'produk_daily ceramois hydra gel', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>frozenset({'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_dna salmon extra marine collagen and hyaluronic acid 30 ml'})</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen glowing new', 'operator_Oktavira'})</t>
+          <t>frozenset({'operator_Oktavira', 'produk_sunscreen glowing new'})</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>frozenset({'operator_Indah', 'produk_facial wash oily acne 110 ml new'})</t>
+          <t>frozenset({'produk_facial wash oily acne 110 ml new', 'operator_Indah'})</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>frozenset({'waktu_Malam', 'produk_serum brightening glowing'})</t>
+          <t>frozenset({'produk_serum brightening glowing', 'waktu_Malam'})</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>frozenset({'produk_sunscreen glowing new', 'waktu_Pagi'})</t>
+          <t>frozenset({'waktu_Pagi', 'produk_sunscreen glowing new'})</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
